--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:49:57+00:00</t>
+    <t>2026-10-09T07:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSEncounter.xlsx
+++ b/StructureDefinition-SEEHDSEncounter.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
